--- a/data/incremental/incremental_05_la_reina_manual.xlsx
+++ b/data/incremental/incremental_05_la_reina_manual.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Restaurantes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG27"/>
+  <dimension ref="A1:AG31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -668,7 +668,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Nativo+La+Reina/@-33.4399398,-70.5352481,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf98005e3acf:0xb38e80ec60c96241!8m2!3d-33.4399398!4d-70.5352481!16s%2Fg%2F11jsy_22np?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Nativo+La+Reina/data=!4m7!3m6!1s0x9662cf98005e3acf:0xb38e80ec60c96241!8m2!3d-33.4399398!4d-70.5352481!16s%2Fg%2F11jsy_22np!19sChIJzzpeAJjPYpYRQWLJYOyAjrM?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,52 +839,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Restaurante Peruano Mar Azul - La Reina</t>
+          <t>Majka bistro</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>378</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Av. Ossa 2294, 7850054 La Reina, Región Metropolitana</t>
+          <t>Av. Príncipe de Gales 7102, 7850291 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9 6520 5381</t>
+          <t>9 9349 8825</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://instagram.com/marazul_lareina?igshid=YmMyMTA2M2Y=</t>
+          <t>http://www.majka.bistro.cl/</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+Peruano+Mar+Azul+-+La+Reina/data=!4m7!3m6!1s0x9662cfd6a982ad4f:0x3ef9442dc655264c!8m2!3d-33.4318791!4d-70.574902!16s%2Fg%2F11rz4qssd2!19sChIJT62CqdbPYpYRTCZVxi1E-T4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Majka+bistro/data=!4m7!3m6!1s0x9662cf0998558ffb:0xa642f0ef4fafcc28!8m2!3d-33.4386378!4d-70.5580849!16s%2Fg%2F11tj6jsqrx!19sChIJ-49VmAnPYpYRKMyvT-_wQqY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-33.4318791</t>
+          <t>-33.4386378</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-70.574902</t>
+          <t>-70.5580849</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,52 +942,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Majka bistro</t>
+          <t>Restaurante Peruano Mar Azul - La Reina</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Av. Príncipe de Gales 7102, 7850291 La Reina, Región Metropolitana</t>
+          <t>Av. Ossa 2294, 7850054 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9 9349 8825</t>
+          <t>9 6520 5381</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>http://www.majka.bistro.cl/</t>
+          <t>https://instagram.com/marazul_lareina?igshid=YmMyMTA2M2Y=</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante peruano</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Majka+bistro/data=!4m7!3m6!1s0x9662cf0998558ffb:0xa642f0ef4fafcc28!8m2!3d-33.4386378!4d-70.5580849!16s%2Fg%2F11tj6jsqrx!19sChIJ-49VmAnPYpYRKMyvT-_wQqY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurante+Peruano+Mar+Azul+-+La+Reina/data=!4m7!3m6!1s0x9662cfd6a982ad4f:0x3ef9442dc655264c!8m2!3d-33.4318791!4d-70.574902!16s%2Fg%2F11rz4qssd2!19sChIJT62CqdbPYpYRTCZVxi1E-T4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-33.4386378</t>
+          <t>-33.4318791</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-70.5580849</t>
+          <t>-70.574902</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1045,32 +1045,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MANTO Restaurant</t>
+          <t>La Fuente Reina</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Av. Alcalde Fernando Castillo Velasco 9047, La Reina, Región Metropolitana</t>
+          <t>Av. Echeñique 8540, La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9 2204 7306</t>
+          <t>9 3239 7261</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://instagram.com/mantorestaurant?utm_medium=copy_link</t>
+          <t>http://www.lafuentereina.cl/</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1080,17 +1080,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/MANTO+Restaurant/data=!4m7!3m6!1s0x9662cfcbb11141c9:0x35a4bac8a7ee582a!8m2!3d-33.4519618!4d-70.538348!16s%2Fg%2F11srb13rs3!19sChIJyUERscvPYpYRKljup8i6pDU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/La+Fuente+Reina/data=!4m7!3m6!1s0x9662ce6ee23a6d41:0x428d73a4f02fff8b!8m2!3d-33.4416745!4d-70.5430468!16s%2Fg%2F11b8_pfyv2!19sChIJQW064m7OYpYRi_8v8KRzjUI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-33.4519618</t>
+          <t>-33.4416745</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-70.538348</t>
+          <t>-70.5430468</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,32 +1148,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>La Fuente Reina</t>
+          <t>MANTO Restaurant</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Av. Echeñique 8540, La Reina, Región Metropolitana</t>
+          <t>Av. Alcalde Fernando Castillo Velasco 9047, La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9 3239 7261</t>
+          <t>9 2204 7306</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>http://www.lafuentereina.cl/</t>
+          <t>https://instagram.com/mantorestaurant?utm_medium=copy_link</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1183,17 +1183,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Fuente+Reina/@-33.4416745,-70.5430468,17z/data=!3m1!4b1!4m6!3m5!1s0x9662ce6ee23a6d41:0x428d73a4f02fff8b!8m2!3d-33.4416745!4d-70.5430468!16s%2Fg%2F11b8_pfyv2?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/MANTO+Restaurant/data=!4m7!3m6!1s0x9662cfcbb11141c9:0x35a4bac8a7ee582a!8m2!3d-33.4519618!4d-70.538348!16s%2Fg%2F11srb13rs3!19sChIJyUERscvPYpYRKljup8i6pDU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-33.4416745</t>
+          <t>-33.4519618</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-70.5430468</t>
+          <t>-70.538348</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Caleta+La+Reina/@-33.4399483,-70.5333349,17z/data=!3m1!4b1!4m6!3m5!1s0x9662ce70da1a5c9b:0x8953fc9ad2c0866e!8m2!3d-33.4399483!4d-70.5333349!16s%2Fg%2F11dxq2tymz?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Caleta+La+Reina/data=!4m7!3m6!1s0x9662ce70da1a5c9b:0x8953fc9ad2c0866e!8m2!3d-33.4399483!4d-70.5333349!16s%2Fg%2F11dxq2tymz!19sChIJm1wa2nDOYpYRbobA0pr8U4k?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Fuente+Carrera/@-33.4533085,-70.5668294,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cfeb359d9aed:0x3ca0a354368ab903!8m2!3d-33.4533085!4d-70.5668294!16s%2Fg%2F11jj4zp3qz?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/La+Fuente+Carrera/data=!4m7!3m6!1s0x9662cfeb359d9aed:0x3ca0a354368ab903!8m2!3d-33.4533085!4d-70.5668294!16s%2Fg%2F11jj4zp3qz!19sChIJ7ZqdNevPYpYRA7mKNlSjoDw?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1865,48 +1865,52 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Casa Pacifico</t>
+          <t>Restaurant Nan Fang La reina</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>435</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Carlos Silva Vildósola 9323, Local 201, 7860379 La Reina, Región Metropolitana</t>
+          <t>Aguas Claras 1601, 7850327 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9 9378 9115</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>(2) 2227 7596</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>http://www.restaurantnanfang.cl/</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante chino</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Casa+Pacifico/@-33.4408983,-70.5334422,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf480e4ced61:0x505493b78ac03af!8m2!3d-33.4408983!4d-70.5334422!16s%2Fg%2F11md3pvkwt?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurant+Nan+Fang+La+reina/data=!4m7!3m6!1s0x9662ce5b153ede8d:0x4587872a3c76776a!8m2!3d-33.4402615!4d-70.5572938!16s%2Fg%2F1tykwlnf!19sChIJjd4-FVvOYpYRand2PCqHh0U?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-33.4408983</t>
+          <t>-33.4402615</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-70.5334422</t>
+          <t>-70.5572938</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1931,12 +1935,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1964,7 +1968,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Restaurant Nan Fang La reina</t>
+          <t>El DUO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1974,42 +1978,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>647</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Aguas Claras 1601, 7850327 La Reina, Región Metropolitana</t>
+          <t>Av. Larraín 6367, 7870176 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(2) 2227 7596</t>
+          <t>9 5324 4393</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>http://www.restaurantnanfang.cl/</t>
+          <t>https://www.elduorestaurant.cl/</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Restaurante chino</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+Nan+Fang+La+reina/data=!4m7!3m6!1s0x9662ce5b153ede8d:0x4587872a3c76776a!8m2!3d-33.4402615!4d-70.5572938!16s%2Fg%2F1tykwlnf!19sChIJjd4-FVvOYpYRand2PCqHh0U?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/El+DUO/data=!4m7!3m6!1s0x9662ce483b4a011b:0x1321b75deaa90219!8m2!3d-33.4530421!4d-70.5639659!16s%2Fg%2F11cns8g5z6!19sChIJGwFKO0jOYpYRGQKp6l23IRM?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-33.4402615</t>
+          <t>-33.4530421</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-70.5572938</t>
+          <t>-70.5639659</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2034,7 +2038,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2067,52 +2071,48 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Casa Valerio Restaurant</t>
+          <t>La Fonda Paisa Terraza Bar</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>206</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Av. Larraín 6580, 7870165 La Reina, Región Metropolitana</t>
+          <t>Av. Alcalde Fernando Castillo Velasco 8517, 7860367 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(2) 2699 6349</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://casavalerio.cl/</t>
-        </is>
-      </c>
+          <t>9 2046 7417</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Bar restaurante</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Casa+Valerio+Restaurant/@-33.4522001,-70.5618285,17z/data=!3m1!4b1!4m6!3m5!1s0x9662c5ad21577f41:0xba98ab0e8dbffc96!8m2!3d-33.4522001!4d-70.5618285!16s%2Fg%2F11b_2njgy4?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/La+Fonda+Paisa+Terraza+Bar/data=!4m7!3m6!1s0x9662cf5e15dd6799:0xfd6686523076d5a1!8m2!3d-33.4514878!4d-70.5428287!16s%2Fg%2F11ppjntz69!19sChIJmWfdFV7PYpYRodV2MFKGZv0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-33.4522001</t>
+          <t>-33.4514878</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-70.5618285</t>
+          <t>-70.5428287</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2170,52 +2170,48 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>La Cabrera Al Paso Egaña</t>
+          <t>Casa Pacifico</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>56</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Av. Larraín 5862, 7870154 La Reina, Región Metropolitana</t>
+          <t>Carlos Silva Vildósola 9323, Local 201, 7860379 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9 3357 9943</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>http://lacabreraalpaso.cl/</t>
-        </is>
-      </c>
+          <t>9 9378 9115</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Restaurante especializado en barbacoa</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Cabrera+Al+Paso+Ega%C3%B1a/data=!4m7!3m6!1s0x9662cf00018543bd:0xa745b446141cd7d0!8m2!3d-33.4522161!4d-70.5691478!16s%2Fg%2F11lydt55qj!19sChIJvUOFAQDPYpYR0NccFEa0Rac?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Casa+Pacifico/data=!4m7!3m6!1s0x9662cf480e4ced61:0x505493b78ac03af!8m2!3d-33.4408983!4d-70.5334422!16s%2Fg%2F11md3pvkwt!19sChIJYe1MDkjPYpYRrwOseDtJBQU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-33.4522161</t>
+          <t>-33.4408983</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-70.5691478</t>
+          <t>-70.5334422</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2240,12 +2236,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2273,52 +2269,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alemán Experto La Reina</t>
+          <t>Casa Valerio Restaurant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Av. Ossa 655, 7870053 La Reina, Región Metropolitana</t>
+          <t>Av. Larraín 6580, 7870165 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9 5451 1718</t>
+          <t>(2) 2699 6349</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.alemanexperto.cl/</t>
+          <t>https://casavalerio.cl/</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante peruano</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Alem%C3%A1n+Experto+La+Reina/data=!4m7!3m6!1s0x9662cf3cb647e3db:0x9eade190733dd480!8m2!3d-33.4476738!4d-70.5712117!16s%2Fg%2F11l72v5qy1!19sChIJ2-NHtjzPYpYRgNQ9c5DhrZ4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Casa+Valerio+Restaurant/data=!4m7!3m6!1s0x9662c5ad21577f41:0xba98ab0e8dbffc96!8m2!3d-33.4522001!4d-70.5618285!16s%2Fg%2F11b_2njgy4!19sChIJQX9XIa3FYpYRlvy_jQ6rmLo?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-33.4476738</t>
+          <t>-33.4522001</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-70.5712117</t>
+          <t>-70.5618285</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2343,7 +2339,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2376,48 +2372,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>La Fonda Paisa Terraza Bar</t>
+          <t>Alemán Experto La Reina</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>704</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Av. Alcalde Fernando Castillo Velasco 8517, 7860367 La Reina, Región Metropolitana</t>
+          <t>Av. Ossa 655, 7870053 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9 2046 7417</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>9 5451 1718</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.alemanexperto.cl/</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bar restaurante</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Fonda+Paisa+Terraza+Bar/@-33.4514878,-70.5428287,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf5e15dd6799:0xfd6686523076d5a1!8m2!3d-33.4514878!4d-70.5428287!16s%2Fg%2F11ppjntz69?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Alem%C3%A1n+Experto+La+Reina/data=!4m7!3m6!1s0x9662cf3cb647e3db:0x9eade190733dd480!8m2!3d-33.4476738!4d-70.5712117!16s%2Fg%2F11l72v5qy1!19sChIJ2-NHtjzPYpYRgNQ9c5DhrZ4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-33.4514878</t>
+          <t>-33.4476738</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-70.5428287</t>
+          <t>-70.5712117</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2475,52 +2475,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>El DUO</t>
+          <t>Lima Limón La Reina</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Av. Larraín 6367, 7870176 La Reina, Región Metropolitana</t>
+          <t>Av. Príncipe de Gales 7218, 7850291 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9 5324 4393</t>
+          <t>(2) 2839 0285</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.elduorestaurant.cl/</t>
+          <t>http://www.limalimonrest.cl/</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante peruano</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/El+DUO/data=!4m7!3m6!1s0x9662ce483b4a011b:0x1321b75deaa90219!8m2!3d-33.4530421!4d-70.5639659!16s%2Fg%2F11cns8g5z6!19sChIJGwFKO0jOYpYRGQKp6l23IRM?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Lima+Lim%C3%B3n+La+Reina/data=!4m7!3m6!1s0x9662ce5b7f2954d1:0xe7f1362d3d2bd41b!8m2!3d-33.4386034!4d-70.5572379!16s%2Fg%2F11c0vldmsf!19sChIJ0VQpf1vOYpYRG9QrPS028ec?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-33.4530421</t>
+          <t>-33.4386034</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-70.5639659</t>
+          <t>-70.5572379</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2578,52 +2578,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lima Limón La Reina</t>
+          <t>La Cabrera Al Paso Egaña</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>481</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Av. Príncipe de Gales 7218, 7850291 La Reina, Región Metropolitana</t>
+          <t>Av. Larraín 5862, 7870154 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(2) 2839 0285</t>
+          <t>9 3357 9943</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>http://www.limalimonrest.cl/</t>
+          <t>http://lacabreraalpaso.cl/</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Restaurante especializado en barbacoa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Lima+Lim%C3%B3n+La+Reina/@-33.4386034,-70.5572379,17z/data=!3m1!4b1!4m6!3m5!1s0x9662ce5b7f2954d1:0xe7f1362d3d2bd41b!8m2!3d-33.4386034!4d-70.5572379!16s%2Fg%2F11c0vldmsf?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/La+Cabrera+Al+Paso+Ega%C3%B1a/data=!4m7!3m6!1s0x9662cf00018543bd:0xa745b446141cd7d0!8m2!3d-33.4522161!4d-70.5691478!16s%2Fg%2F11lydt55qj!19sChIJvUOFAQDPYpYR0NccFEa0Rac?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-33.4386034</t>
+          <t>-33.4522161</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-70.5572379</t>
+          <t>-70.5691478</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2681,48 +2681,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>El Japonés - MallPlaza Egaña</t>
+          <t>Rossie La Loca - La Reina</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Av. Larraín 5862, 7870154 La Reina, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Aguas Claras 1700, Local 12, 8933618 La Reina, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>9 8319 0114</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://eljaponeschile.com/locales/</t>
+          <t>http://www.rossielaloca.cl/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Bar</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/El+Japon%C3%A9s+-+MallPlaza+Ega%C3%B1a/@-33.4524377,-70.5694704,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cf85bf55bc7d:0xdc8042e989203a0b!8m2!3d-33.4524377!4d-70.5694704!16s%2Fg%2F11shx7yg7v?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Rossie+La+Loca+-+La+Reina/data=!4m7!3m6!1s0x9662cfea2a83a653:0xe5457febea8db8cc!8m2!3d-33.4391642!4d-70.5568456!16s%2Fg%2F11wbdssxp8!19sChIJU6aDKurPYpYRzLiN6ut_ReU?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-33.4524377</t>
+          <t>-33.4391642</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-70.5694704</t>
+          <t>-70.5568456</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2747,17 +2751,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sin teléfono</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
@@ -2775,61 +2779,57 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>Sin teléfono visible</t>
-        </is>
-      </c>
+      <c r="AG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mattarello</t>
+          <t>Mister Fish La Reina</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>439</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Av. Príncipe de Gales 6560, 7850000 La Reina, Región Metropolitana</t>
+          <t>Av. Francisco Bilbao 5359, 7850038 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9 5818 0896</t>
+          <t>(2) 3339 9289</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>http://www.mattarello.cl/</t>
+          <t>http://www.misterfish.cl/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Restaurante italiano</t>
+          <t>Pub restaurante</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Mattarello/data=!4m7!3m6!1s0x9662ce50c17b5211:0x7401100e212ac2cd!8m2!3d-33.4383135!4d-70.5641203!16s%2Fg%2F11gfdv9jck!19sChIJEVJ7wVDOYpYRzcIqIQ4QAXQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Mister+Fish+La+Reina/data=!4m7!3m6!1s0x9662cfc0eace1ae3:0xdac4b383858abb36!8m2!3d-33.4314761!4d-70.578257!16s%2Fg%2F11ls_nm_xd!19sChIJ4xrO6sDPYpYRNruKhYOzxNo?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-33.4383135</t>
+          <t>-33.4314761</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-70.5641203</t>
+          <t>-70.578257</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2887,7 +2887,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>El Gordito</t>
+          <t>Mattarello</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2897,42 +2897,42 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Av. Larraín 6011, 7870203 La Reina, Región Metropolitana</t>
+          <t>Av. Príncipe de Gales 6560, 7850000 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9 6663 3388</t>
+          <t>9 5818 0896</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/elgorditotenedorlibr?igsh=MWNyb2ZrazdxMXB1dA==</t>
+          <t>http://www.mattarello.cl/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante italiano</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/El+Gordito/@-33.4535739,-70.5678384,17z/data=!3m1!4b1!4m6!3m5!1s0x9662cfc00f2689bb:0x6828f0b054308a05!8m2!3d-33.4535739!4d-70.5678384!16s%2Fg%2F11lnjxsn6g?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Mattarello/data=!4m7!3m6!1s0x9662ce50c17b5211:0x7401100e212ac2cd!8m2!3d-33.4383135!4d-70.5641203!16s%2Fg%2F11gfdv9jck!19sChIJEVJ7wVDOYpYRzcIqIQ4QAXQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-33.4535739</t>
+          <t>-33.4383135</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-70.5678384</t>
+          <t>-70.5641203</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2990,32 +2990,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sol Sublime Restaurant</t>
+          <t>El Japonés - MallPlaza Egaña</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Av. Príncipe de Gales 6580, 7850286 Santiago, La Reina, Región Metropolitana</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>(2) 2226 1145</t>
-        </is>
-      </c>
+          <t>Av. Larraín 5862, 7870154 La Reina, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>http://www.solsublime.cl/</t>
+          <t>https://eljaponeschile.com/locales/</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3025,17 +3021,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sol+Sublime+Restaurant/@-33.4383546,-70.563731,17z/data=!3m1!4b1!4m6!3m5!1s0x9662ce50d8cacb11:0xddaab3805dc26123!8m2!3d-33.4383546!4d-70.563731!16s%2Fg%2F11b5wffrkb?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/El+Japon%C3%A9s+-+MallPlaza+Ega%C3%B1a/data=!4m7!3m6!1s0x9662cf85bf55bc7d:0xdc8042e989203a0b!8m2!3d-33.4524377!4d-70.5694704!16s%2Fg%2F11shx7yg7v!19sChIJfbxVv4XPYpYRCzogielCgNw?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-33.4383546</t>
+          <t>-33.4524377</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-70.563731</t>
+          <t>-70.5694704</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3060,12 +3056,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Sin teléfono</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3088,12 +3084,16 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sabores de Lima</t>
+          <t>Sol Sublime Restaurant</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3103,42 +3103,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>678</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Av. Nueva - Av. Alcalde Fernando Castillo Velasco 9097, 7850000 La Reina, Región Metropolitana</t>
+          <t>Av. Príncipe de Gales 6580, 7850286 Santiago, La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(2) 2275 3068</t>
+          <t>(2) 2226 1145</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>http://www.saboresdelima.cl/</t>
+          <t>http://www.solsublime.cl/</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sabores+de+Lima/@-33.4521068,-70.5379765,17z/data=!3m1!4b1!4m6!3m5!1s0x9662ce0d786dcbdf:0x9dade29717f28e9c!8m2!3d-33.4521068!4d-70.5379765!16s%2Fg%2F11g8pbzph6?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Sol+Sublime+Restaurant/data=!4m7!3m6!1s0x9662ce50d8cacb11:0xddaab3805dc26123!8m2!3d-33.4383546!4d-70.563731!16s%2Fg%2F11b5wffrkb!19sChIJEcvK2FDOYpYRI2HCXYCzqt0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-33.4521068</t>
+          <t>-33.4383546</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-70.5379765</t>
+          <t>-70.563731</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3196,52 +3196,52 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>El cha cha pollo</t>
+          <t>El Gordito</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>518</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Av. Larraín 6812, 7850000 La Reina, Región Metropolitana</t>
+          <t>Av. Larraín 6011, 7870203 La Reina, Región Metropolitana</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>9 4750 2847</t>
+          <t>9 6663 3388</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://elchachapollo.cl/</t>
+          <t>https://www.instagram.com/elgorditotenedorlibr?igsh=MWNyb2ZrazdxMXB1dA==</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Restaurante de comida rápida</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/El+cha+cha+pollo/data=!4m7!3m6!1s0x9662cf2357297345:0xcb53e6f5eec1f4cb!8m2!3d-33.4520411!4d-70.5592535!16s%2Fg%2F11nnt2t649!19sChIJRXMpVyPPYpYRy_TB7vXmU8s?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/El+Gordito/data=!4m7!3m6!1s0x9662cfc00f2689bb:0x6828f0b054308a05!8m2!3d-33.4535739!4d-70.5678384!16s%2Fg%2F11lnjxsn6g!19sChIJu4kmD8DPYpYRBYowVLDwKGg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-33.4520411</t>
+          <t>-33.4535739</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-70.5592535</t>
+          <t>-70.5678384</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3294,14 +3294,422 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr">
+      <c r="AG27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RESTAURANT COSTANAZCA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Av, Av. Príncipe de Gales 6777, 7850308 La Reina, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>(2) 2277 2184</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Restaurante peruano</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/RESTAURANT+COSTANAZCA/data=!4m7!3m6!1s0x9662ce5a771edb9b:0x53a370991571e262!8m2!3d-33.4388308!4d-70.5619835!16s%2Fg%2F1hjh6cqf7!19sChIJm9sed1rOYpYRYuJxFZlwo1M?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-33.4388308</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-70.5619835</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Misky Mikuy</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Monseñor Edwards 1739, 7850287 La Reina, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>(2) 2277 2574</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>http://www.miskymikuyrest.cl/</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Restaurante peruano</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Misky+Mikuy/data=!4m7!3m6!1s0x9662ce5a6dc11513:0xa70f614d8b5e28ea!8m2!3d-33.4380989!4d-70.560913!16s%2Fg%2F12vsbnns3!19sChIJExXBbVrOYpYR6ihei01hD6c?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-33.4380989</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-70.560913</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>El cha cha pollo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Av. Larraín 6812, 7850000 La Reina, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>9 4750 2847</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://elchachapollo.cl/</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Restaurante de comida rápida</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/El+cha+cha+pollo/data=!4m7!3m6!1s0x9662cf2357297345:0xcb53e6f5eec1f4cb!8m2!3d-33.4520411!4d-70.5592535!16s%2Fg%2F11nnt2t649!19sChIJRXMpVyPPYpYRy_TB7vXmU8s?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-33.4520411</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-70.5592535</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr">
         <is>
           <t>Revisar: parece comida rapida</t>
         </is>
       </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sabores de Lima</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Av. Nueva - Av. Alcalde Fernando Castillo Velasco 9097, 7850000 La Reina, Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>(2) 2275 3068</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>http://www.saboresdelima.cl/</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Restaurante peruano</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Sabores+de+Lima/data=!4m7!3m6!1s0x9662ce0d786dcbdf:0x9dade29717f28e9c!8m2!3d-33.4521068!4d-70.5379765!16s%2Fg%2F11g8pbzph6!19sChIJ38tteA3OYpYRnI7yF5firZ0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-33.4521068</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-70.5379765</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>La Reina</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG27"/>
+  <autoFilter ref="A1:AG31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>